--- a/templates/excel/partner-output-ledger.xlsx
+++ b/templates/excel/partner-output-ledger.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly_Variable" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Partner_Dashboard" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Partner_Multipliers_Snapshot" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="_metadata" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="_metadata" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="output_log">Output_Log!$A:$M</definedName>
@@ -1095,184 +1095,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># partner-output-ledger.xlsx</t>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spec_version</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
+          <t>generation_date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Records daily output per partner. Source of truth for monthly variable pay (Routine R3) and weekly Business Review agenda (Routine R2).</t>
+          <t>oot_version</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>WRITTEN BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>- Routine R1 (Daily Output Capture, daily 18:00) — appends rows to Output_Log.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>READ BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>- Routine R2 (Weekly BR Prep) — surfaces notable outputs, blockers, KPI movements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>- Routine R3 (Monthly Variable Calc) — locks previous month's Output_Log; populates Monthly_Variable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>- Routine R4 (Quarterly Long-Tail Settlement) — references Output_Log for outputs eligible for long-tail entitlements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REVIEWED BY</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>- Each partner: monthly, before Variable sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>- Founder: monthly, for Variable approval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>- Friday Business Review: weekly, in the standing agenda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DESIGN DECISION — column J (partner_multiplier) is NOT a formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>The X1.J value is written by R1 at row-append time. R1 reads X2's output_multiplier at runtime and writes the resolved number. This avoids the unreliable cross-workbook formula pattern in openpyxl. The Partner_Multipliers_Snapshot sheet is a read-only mirror refreshed monthly by R3 — it is not consumed by any formula.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DESIGN DECISION — AI-authored output is paid at full rate at month-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>The L column formula does NOT discount by ai_authored_pct. The framework's correction discipline is the rework-within-30d zero-out. AI-assisted output requiring rework "was not actually output, it was just typing."</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DO NOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>- Edit Output_Log rows that have been included in a paid Monthly_Variable. Use the renegotiation flow per Skill Pack S3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>- Bypass the rework_within_30d field. The YOLO model's correction discipline depends on it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>- Aggregate values in ways that obscure individual partner attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>- Modify column J via formula — the cross-workbook discipline requires Routine writes.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>X1</t>
         </is>
       </c>
     </row>
@@ -1287,66 +1169,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
+          <t># partner-output-ledger.xlsx</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spec_version</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generation_date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
+          <t>PURPOSE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oot_version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
+          <t>Records daily output per partner. Source of truth for monthly variable pay (Routine R3) and weekly Business Review agenda (Routine R2).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>X1</t>
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WRITTEN BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>- Routine R1 (Daily Output Capture, daily 18:00) — appends rows to Output_Log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>READ BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>- Routine R2 (Weekly BR Prep) — surfaces notable outputs, blockers, KPI movements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>- Routine R3 (Monthly Variable Calc) — locks previous month's Output_Log; populates Monthly_Variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>- Routine R4 (Quarterly Long-Tail Settlement) — references Output_Log for outputs eligible for long-tail entitlements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REVIEWED BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>- Each partner: monthly, before Variable sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>- Founder: monthly, for Variable approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>- Friday Business Review: weekly, in the standing agenda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DESIGN DECISION — column J (partner_multiplier) is NOT a formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>The X1.J value is written by R1 at row-append time. R1 reads X2's output_multiplier at runtime and writes the resolved number. This avoids the unreliable cross-workbook formula pattern in openpyxl. The Partner_Multipliers_Snapshot sheet is a read-only mirror refreshed monthly by R3 — it is not consumed by any formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DESIGN DECISION — AI-authored output is paid at full rate at month-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>The L column formula does NOT discount by ai_authored_pct. The framework's correction discipline is the rework-within-30d zero-out. AI-assisted output requiring rework "was not actually output, it was just typing."</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DO NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>- Edit Output_Log rows that have been included in a paid Monthly_Variable. Use the renegotiation flow per Skill Pack S3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>- Bypass the rework_within_30d field. The YOLO model's correction discipline depends on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>- Aggregate values in ways that obscure individual partner attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>- Modify column J via formula — the cross-workbook discipline requires Routine writes.</t>
         </is>
       </c>
     </row>

--- a/templates/excel/partner-output-ledger.xlsx
+++ b/templates/excel/partner-output-ledger.xlsx
@@ -15,7 +15,7 @@
     <sheet name="README" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="output_log">Output_Log!$A:$M</definedName>
+    <definedName name="output_log">Output_Log!$A:$N</definedName>
     <definedName name="value_envelope_table">Output_Log!$O$1:$P$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,6 +458,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
@@ -528,6 +529,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>value_tier</t>
@@ -591,13 +597,16 @@
         <v/>
       </c>
       <c r="L2">
-        <f>K2*J2*IF(I2="Yes",0,1)</f>
+        <f>K2*J2*N2*IF(I2="Yes",0,1)</f>
         <v/>
       </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Initial sample data</t>
         </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -660,10 +669,13 @@
         <v/>
       </c>
       <c r="L3">
-        <f>K3*J3*IF(I3="Yes",0,1)</f>
+        <f>K3*J3*N3*IF(I3="Yes",0,1)</f>
         <v/>
       </c>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>L</t>
@@ -725,13 +737,16 @@
         <v/>
       </c>
       <c r="L4">
-        <f>K4*J4*IF(I4="Yes",0,1)</f>
+        <f>K4*J4*N4*IF(I4="Yes",0,1)</f>
         <v/>
       </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>First closed deal</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1169,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1318,33 +1333,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DO NOT</t>
+          <t>CO-AUTHORSHIP WEIGHT — column N (ADR-005)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>- Edit Output_Log rows that have been included in a paid Monthly_Variable. Use the renegotiation flow per Skill Pack S3.</t>
+          <t>Column N (weight) is a number in (0, 1], default 1.0. For a co-authored output R1 writes one row per co-author with weight = 1/N (or the output spec's attribution_split fractions). The L formula (=K*J*N*IF(rework)) shares the envelope across co-authors instead of paying each 100%. Two co-authors on one L-tier output receive €250 each, not €500 each.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>- Bypass the rework_within_30d field. The YOLO model's correction discipline depends on it.</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>- Aggregate values in ways that obscure individual partner attribution.</t>
+          <t>DO NOT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
+        <is>
+          <t>- Edit Output_Log rows that have been included in a paid Monthly_Variable. Use the renegotiation flow per Skill Pack S3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>- Bypass the rework_within_30d field. The YOLO model's correction discipline depends on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>- Aggregate values in ways that obscure individual partner attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>- Modify column J via formula — the cross-workbook discipline requires Routine writes.</t>
         </is>
